--- a/test/excel/keep/struct-open/wide-delete-from-col.xlsx
+++ b/test/excel/keep/struct-open/wide-delete-from-col.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-62166/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-20228/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA84769-885D-D24D-9C09-EFFBD9D96D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15436E22-C045-5D44-BCEF-96A9DA1919FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -316,8 +316,8 @@
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
@@ -352,8 +352,8 @@
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
